--- a/5° Período/Estatística/3 - Prova 10 04 2021/Estatística P1 Tabelas.xlsx
+++ b/5° Período/Estatística/3 - Prova 10 04 2021/Estatística P1 Tabelas.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gustavo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Exercicios-UNIVALI\5° Período\Estatística\3 - Prova 10 04 2021\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,21 +32,6 @@
     <t>Concentração (mg/L)</t>
   </si>
   <si>
-    <t>[14.3166, 14.6333)</t>
-  </si>
-  <si>
-    <t>[14.6333, 14.95)</t>
-  </si>
-  <si>
-    <t>[14.95, 15.2667)</t>
-  </si>
-  <si>
-    <t>[15.2667, 15.5833)</t>
-  </si>
-  <si>
-    <t>[15.5833, 15.9]</t>
-  </si>
-  <si>
     <t>14,1583</t>
   </si>
   <si>
@@ -59,9 +44,6 @@
     <t>15,1083</t>
   </si>
   <si>
-    <t>[14, 14.3166)</t>
-  </si>
-  <si>
     <t>15,425</t>
   </si>
   <si>
@@ -129,13 +111,31 @@
   </si>
   <si>
     <t>QUESTÃO 1</t>
+  </si>
+  <si>
+    <t>[14, 14.32)</t>
+  </si>
+  <si>
+    <t>[14.32, 14.64)</t>
+  </si>
+  <si>
+    <t>[14.64, 14.95)</t>
+  </si>
+  <si>
+    <t>[14.95, 15.27)</t>
+  </si>
+  <si>
+    <t>[15.27, 15.59)</t>
+  </si>
+  <si>
+    <t>[15.59, 15.9]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +170,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="4">
@@ -219,7 +225,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -238,6 +244,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -360,22 +369,22 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>[14, 14.3166)</c:v>
+                  <c:v>[14, 14.32)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>[14.3166, 14.6333)</c:v>
+                  <c:v>[14.32, 14.64)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>[14.6333, 14.95)</c:v>
+                  <c:v>[14.64, 14.95)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>[14.95, 15.2667)</c:v>
+                  <c:v>[14.95, 15.27)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>[15.2667, 15.5833)</c:v>
+                  <c:v>[15.27, 15.59)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>[15.5833, 15.9]</c:v>
+                  <c:v>[15.59, 15.9]</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -417,8 +426,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="0"/>
-        <c:axId val="288132800"/>
-        <c:axId val="288139872"/>
+        <c:axId val="427689472"/>
+        <c:axId val="427693824"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -488,11 +497,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="288132800"/>
-        <c:axId val="288139872"/>
+        <c:axId val="427689472"/>
+        <c:axId val="427693824"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="288132800"/>
+        <c:axId val="427689472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -585,7 +594,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="288139872"/>
+        <c:crossAx val="427693824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -593,7 +602,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="288139872"/>
+        <c:axId val="427693824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -686,7 +695,7 @@
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="288132800"/>
+        <c:crossAx val="427689472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -1584,7 +1593,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1595,30 +1604,30 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
+      <c r="A3" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
         <v>9</v>
@@ -1640,11 +1649,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
+      <c r="A4" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
         <v>4</v>
@@ -1666,11 +1675,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
+      <c r="A5" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
         <v>4</v>
@@ -1692,11 +1701,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
+      <c r="A6" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
         <v>3</v>
@@ -1718,11 +1727,11 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
+      <c r="A7" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1744,11 +1753,11 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
+      <c r="A8" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2">
         <v>5</v>
@@ -1771,16 +1780,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1791,49 +1800,57 @@
         <v>14.6</v>
       </c>
       <c r="C24" s="5">
-        <v>0.35310000000000002</v>
+        <v>0.35314166666666602</v>
       </c>
       <c r="D24" s="5">
-        <v>0.59419999999999995</v>
+        <v>0.59425723947350095</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D25" s="5">
+        <v>0.59</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D30" s="5">
         <v>7.0000000000000007E-2</v>
@@ -1861,24 +1878,24 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1892,15 +1909,15 @@
         <v>513</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D37" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E37" s="5">
         <v>42</v>
